--- a/coreweave/docs/reports/20261008_coreweave_v4.7_收入錨定.xlsx
+++ b/coreweave/docs/reports/20261008_coreweave_v4.7_收入錨定.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="196">
   <si>
     <r>
       <rPr>
@@ -256,7 +256,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）；長約占比＝</t>
+      <t xml:space="preserve">）；</t>
     </r>
     <r>
       <rPr>
@@ -266,7 +266,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">RPO </t>
+      <t xml:space="preserve">k</t>
     </r>
     <r>
       <rPr>
@@ -275,7 +275,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">涵蓋的產能 </t>
+      <t xml:space="preserve">＝隨需占比 </t>
     </r>
     <r>
       <rPr>
@@ -285,7 +285,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">÷ </t>
+      <t xml:space="preserve">× k_</t>
     </r>
     <r>
       <rPr>
@@ -294,7 +294,55 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">在役計費產能</t>
+      <t xml:space="preserve">現貨＋（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需占比）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約，隨需占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0%</t>
     </r>
   </si>
   <si>
@@ -466,9 +514,6 @@
     <t xml:space="preserve">賣出</t>
   </si>
   <si>
-    <t xml:space="preserve">中立</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -780,16 +825,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v4.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">長約占比</t>
+      <t xml:space="preserve">v4.7 RPO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">覆蓋率（對照，不驅動）</t>
     </r>
   </si>
   <si>
@@ -1546,38 +1591,32 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">在役計費產能（未截斷）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">長約占比（截斷於 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0–100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，含調整）</t>
-    </r>
+      <t xml:space="preserve">在役計費產能（對照，不驅動）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約（依目前成本情境重算）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">隨需占比（輸入）</t>
   </si>
   <si>
     <r>
@@ -1606,7 +1645,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（長約占比 </t>
+      <t xml:space="preserve">（隨需占比 </t>
     </r>
     <r>
       <rPr>
@@ -1625,7 +1664,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">長約 ＋（</t>
+      <t xml:space="preserve">現貨 ＋（</t>
     </r>
     <r>
       <rPr>
@@ -1644,7 +1683,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">長約占比）</t>
+      <t xml:space="preserve">隨需占比）</t>
     </r>
     <r>
       <rPr>
@@ -1663,7 +1702,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">現貨）</t>
+      <t xml:space="preserve">長約）</t>
     </r>
   </si>
   <si>
@@ -2632,7 +2671,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">筆同一供應商，只支持區間</t>
+      <t xml:space="preserve">筆同一供應商，只支持區間；三筆長約中位數＝本筆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（敏感度）</t>
     </r>
   </si>
   <si>
@@ -3011,7 +3069,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">自有廠房；只列不用</t>
+      <t xml:space="preserve">自有廠房；只列不用；納入三筆長約中位數的敏感度</t>
     </r>
   </si>
   <si>
@@ -5337,6 +5395,46 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">0.89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（三筆長約中位數）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">1.00</t>
     </r>
   </si>
@@ -5345,6 +5443,34 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -5368,10 +5494,47 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.50</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">1.76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隨需占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -5399,58 +5562,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2.30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">長約占比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-20pt</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">長約占比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（新簽約全視為長約）</t>
+      <t xml:space="preserve">1.76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -5702,26 +5823,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（長約／現貨依 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RPO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涵蓋加權）</t>
+      <t xml:space="preserve">（隨需占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -6256,114 +6434,114 @@
         <v>43.9927732107067</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>91.2392623465329</v>
+        <v>13.9805355188478</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">C5-B5</f>
-        <v>47.2464891358262</v>
+        <v>-30.0122376918589</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>32.6541307880956</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>30.2923738695558</v>
+        <v>54.8411224358677</v>
       </c>
       <c r="I5" s="5" t="n">
         <f aca="false">H5-G5</f>
-        <v>-2.36175691853976</v>
+        <v>22.1869916477721</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>29.6784724968844</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>98.0184876310382</v>
+        <v>5.24785180769839</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">C6-B6</f>
-        <v>68.3400151341538</v>
+        <v>-24.430620689186</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>81.5717800280631</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>67.5253862342037</v>
+        <v>104.768016723937</v>
       </c>
       <c r="I6" s="5" t="n">
         <f aca="false">H6-G6</f>
-        <v>-14.0463937938595</v>
+        <v>23.1962366958739</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>19.9489203041466</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>131.856409498704</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">C7-B7</f>
-        <v>111.907489194557</v>
+        <v>-19.9489203041466</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>157.94628018574</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>118.117303569076</v>
+        <v>183.494127989618</v>
       </c>
       <c r="I7" s="5" t="n">
         <f aca="false">H7-G7</f>
-        <v>-39.8289766166647</v>
+        <v>25.547847803878</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>11.2</v>
@@ -6383,7 +6561,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>11.0739648243069</v>
@@ -6403,7 +6581,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>0.76</v>
@@ -6412,24 +6590,24 @@
         <v>0.76</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.849580659826248</v>
+        <v>0.76</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1.0480908566102</v>
+        <v>0.76</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1.33792283192951</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>1</v>
+        <v>2.16382546275903</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>1.37415069619266</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0.910419340173752</v>
@@ -6443,7 +6621,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>8.41621326647324</v>
@@ -6452,18 +6630,18 @@
         <v>8.78712095313968</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10.1287899807039</v>
+        <v>9.06079993265069</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>12.6972629009115</v>
+        <v>9.20714052968951</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>16.465206537042</v>
+        <v>9.35297363159967</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="8" t="n">
         <f aca="false">B11*B12-B14</f>
@@ -6510,33 +6688,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>30</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>10.0453731343284</v>
@@ -6556,10 +6734,10 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>7.63760535510633</v>
@@ -6568,21 +6746,21 @@
         <v>8.16155930610514</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>8.9976644071634</v>
+        <v>8.42092820744111</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>10.3095868834926</v>
+        <v>8.41443808605361</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>12.1181368502249</v>
+        <v>8.140874300043</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="6" t="n">
         <f aca="false">C3-C2</f>
@@ -6594,23 +6772,23 @@
       </c>
       <c r="E4" s="6" t="n">
         <f aca="false">E3-E2</f>
-        <v>-1.36748167979312</v>
+        <v>-1.94421787951541</v>
       </c>
       <c r="F4" s="6" t="n">
         <f aca="false">F3-F2</f>
-        <v>0.53274094599257</v>
+        <v>-1.36240785144639</v>
       </c>
       <c r="G4" s="6" t="n">
         <f aca="false">G3-G2</f>
-        <v>3.12937637403442</v>
+        <v>-0.847886176147474</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>9.68716417910448</v>
@@ -6630,10 +6808,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>7.27939639988245</v>
@@ -6642,21 +6820,21 @@
         <v>7.75751890206473</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>8.47592527672861</v>
+        <v>7.89918907700633</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>9.60958688349257</v>
+        <v>7.71443808605361</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>11.213374945463</v>
+        <v>7.2361123952811</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">C6-C5</f>
@@ -6668,23 +6846,23 @@
       </c>
       <c r="E7" s="6" t="n">
         <f aca="false">E6-E5</f>
-        <v>-1.36748167979312</v>
+        <v>-1.94421787951541</v>
       </c>
       <c r="F7" s="6" t="n">
         <f aca="false">F6-F5</f>
-        <v>0.532740945992574</v>
+        <v>-1.36240785144639</v>
       </c>
       <c r="G7" s="6" t="n">
         <f aca="false">G6-G5</f>
-        <v>3.12937637403442</v>
+        <v>-0.847886176147476</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>4.24396782571711</v>
@@ -6704,10 +6882,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>4.11118995206681</v>
@@ -6716,21 +6894,21 @@
         <v>4.19615215761624</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4.00872292276628</v>
+        <v>3.97691844107286</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3.94337943898433</v>
+        <v>3.83887026258188</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3.90690754710354</v>
+        <v>3.68757889385079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">C9-C8</f>
@@ -6742,23 +6920,23 @@
       </c>
       <c r="E10" s="6" t="n">
         <f aca="false">E9-E8</f>
-        <v>-0.0754106402060666</v>
+        <v>-0.107215121899489</v>
       </c>
       <c r="F10" s="6" t="n">
         <f aca="false">F9-F8</f>
-        <v>0.0293783356625021</v>
+        <v>-0.075130840739956</v>
       </c>
       <c r="G10" s="6" t="n">
         <f aca="false">G9-G8</f>
-        <v>0.172571434995295</v>
+        <v>-0.0467572182574521</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>5.80140530861125</v>
@@ -6778,10 +6956,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>3.52641540303952</v>
@@ -6790,21 +6968,21 @@
         <v>3.96540714848889</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>4.98894148439711</v>
+        <v>4.44400976636825</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>6.36620744450824</v>
+        <v>4.57556782347173</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>8.21122930312136</v>
+        <v>4.45329540619221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">C12-C11</f>
@@ -6816,23 +6994,23 @@
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">E12-E11</f>
-        <v>-1.29207103958706</v>
+        <v>-1.83700275761592</v>
       </c>
       <c r="F13" s="6" t="n">
         <f aca="false">F12-F11</f>
-        <v>0.503362610330073</v>
+        <v>-1.28727701070643</v>
       </c>
       <c r="G13" s="6" t="n">
         <f aca="false">G12-G11</f>
-        <v>2.95680493903913</v>
+        <v>-0.801128957890023</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>-2.80615562866419</v>
@@ -6852,10 +7030,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>-5.18807878300777</v>
@@ -6864,21 +7042,21 @@
         <v>-5.02063096108832</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-3.01450278869469</v>
+        <v>-3.63319499225971</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-1.13436682382</v>
+        <v>-2.98862486363145</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.930437623613928</v>
+        <v>-2.88808524357707</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="6" t="n">
         <f aca="false">C15-C14</f>
@@ -6890,23 +7068,23 @@
       </c>
       <c r="E16" s="6" t="n">
         <f aca="false">E15-E14</f>
-        <v>-1.40566406944058</v>
+        <v>-2.02435627300561</v>
       </c>
       <c r="F16" s="6" t="n">
         <f aca="false">F15-F14</f>
-        <v>0.405388622081409</v>
+        <v>-1.44886941773004</v>
       </c>
       <c r="G16" s="6" t="n">
         <f aca="false">G15-G14</f>
-        <v>2.8634963788023</v>
+        <v>-0.955026488388697</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>1675</v>
@@ -6926,10 +7104,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>1675</v>
@@ -6949,10 +7127,10 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="6" t="n">
         <f aca="false">C18-C17</f>
@@ -6977,10 +7155,10 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>11.2</v>
@@ -7000,10 +7178,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>8.41621326647324</v>
@@ -7012,21 +7190,21 @@
         <v>8.78712095313968</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>9.77135471571617</v>
+        <v>9.0422975541778</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>11.7202982930551</v>
+        <v>9.15794138366193</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>15.0376329077242</v>
+        <v>9.27055497484596</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="6" t="n">
         <f aca="false">C21-C20</f>
@@ -7038,23 +7216,23 @@
       </c>
       <c r="E22" s="6" t="n">
         <f aca="false">E21-E20</f>
-        <v>-1.72864528428383</v>
+        <v>-2.4577024458222</v>
       </c>
       <c r="F22" s="6" t="n">
         <f aca="false">F21-F20</f>
-        <v>0.720298293055111</v>
+        <v>-1.84205861633807</v>
       </c>
       <c r="G22" s="6" t="n">
         <f aca="false">G21-G20</f>
-        <v>4.5376329077242</v>
+        <v>-1.22944502515404</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>10.64</v>
@@ -7074,10 +7252,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>7.99540260314958</v>
@@ -7086,21 +7264,21 @@
         <v>8.3477649054827</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>9.1850734327732</v>
+        <v>8.49975970092713</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>10.8998774125413</v>
+        <v>8.51688548680559</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>13.8346222751063</v>
+        <v>8.52891057685828</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="6" t="n">
         <f aca="false">C24-C23</f>
@@ -7112,23 +7290,23 @@
       </c>
       <c r="E25" s="6" t="n">
         <f aca="false">E24-E23</f>
-        <v>-1.6249265672268</v>
+        <v>-2.31024029907287</v>
       </c>
       <c r="F25" s="6" t="n">
         <f aca="false">F24-F23</f>
-        <v>0.669877412541249</v>
+        <v>-1.71311451319441</v>
       </c>
       <c r="G25" s="6" t="n">
         <f aca="false">G24-G23</f>
-        <v>4.17462227510626</v>
+        <v>-1.13108942314172</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>11.0739648243069</v>
@@ -7148,10 +7326,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>11.0739648243069</v>
@@ -7171,10 +7349,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6" t="n">
         <f aca="false">C27-C26</f>
@@ -7199,10 +7377,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>1.01138121510161</v>
@@ -7222,10 +7400,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>0.76</v>
@@ -7234,21 +7412,21 @@
         <v>0.76</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.821276842467229</v>
+        <v>0.76</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.972645087968463</v>
+        <v>0.76</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1.23278498869592</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="6" t="n">
         <f aca="false">C30-C29</f>
@@ -7260,23 +7438,23 @@
       </c>
       <c r="E31" s="6" t="n">
         <f aca="false">E30-E29</f>
-        <v>-0.145291659358048</v>
+        <v>-0.206568501825277</v>
       </c>
       <c r="F31" s="6" t="n">
         <f aca="false">F30-F29</f>
-        <v>0.0597761745558353</v>
+        <v>-0.152868913412628</v>
       </c>
       <c r="G31" s="6" t="n">
         <f aca="false">G30-G29</f>
-        <v>0.371995098376265</v>
+        <v>-0.100789890319657</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0.672768</v>
@@ -7296,10 +7474,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>0.672768</v>
@@ -7319,10 +7497,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="6" t="n">
         <f aca="false">C33-C32</f>
@@ -7347,10 +7525,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>0.936206901352657</v>
@@ -7370,10 +7548,10 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>0.936206901352657</v>
@@ -7393,10 +7571,10 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C37" s="6" t="n">
         <f aca="false">C36-C35</f>
@@ -7421,10 +7599,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>0.325</v>
@@ -7444,10 +7622,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>0.325</v>
@@ -7467,10 +7645,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C40" s="6" t="n">
         <f aca="false">C39-C38</f>
@@ -7495,10 +7673,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>0.156034483558776</v>
@@ -7518,10 +7696,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>0.156034483558776</v>
@@ -7541,10 +7719,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6" t="n">
         <f aca="false">C42-C41</f>
@@ -7569,10 +7747,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>1.6</v>
@@ -7592,10 +7770,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>1.6</v>
@@ -7615,10 +7793,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C46" s="6" t="n">
         <f aca="false">C45-C44</f>
@@ -7643,10 +7821,10 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="9" t="n">
         <v>0.577520140967778</v>
@@ -7666,10 +7844,10 @@
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48" s="9" t="n">
         <v>0.46171741522123</v>
@@ -7678,44 +7856,44 @@
         <v>0.485863913960979</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.554470722471625</v>
+        <v>0.527733957218793</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.617503641654316</v>
+        <v>0.543775802576222</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.677598330882768</v>
+        <v>0.547029132505914</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>30</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>10.0453731343284</v>
@@ -7735,10 +7913,10 @@
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>7.63760535510633</v>
@@ -7747,21 +7925,21 @@
         <v>8.16155930610514</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>9.24469028632138</v>
+        <v>8.3998358502713</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>10.8835388846575</v>
+        <v>8.30204726630873</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>12.7665605913228</v>
+        <v>7.86163652282644</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C53" s="6" t="n">
         <f aca="false">C52-C51</f>
@@ -7773,23 +7951,23 @@
       </c>
       <c r="E53" s="6" t="n">
         <f aca="false">E52-E51</f>
-        <v>-1.08472253058003</v>
+        <v>-1.92957696663011</v>
       </c>
       <c r="F53" s="6" t="n">
         <f aca="false">F52-F51</f>
-        <v>1.25539149829389</v>
+        <v>-1.32610012005491</v>
       </c>
       <c r="G53" s="6" t="n">
         <f aca="false">G52-G51</f>
-        <v>4.11388174516891</v>
+        <v>-0.791042323327411</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>9.68716417910448</v>
@@ -7809,10 +7987,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="6" t="n">
         <v>7.27939639988245</v>
@@ -7821,21 +7999,21 @@
         <v>7.75751890206473</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>8.73764803280026</v>
+        <v>7.89279359675017</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>10.2471752482939</v>
+        <v>7.66568362994509</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>12.0357913605535</v>
+        <v>7.13086729205721</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C56" s="6" t="n">
         <f aca="false">C55-C54</f>
@@ -7847,23 +8025,23 @@
       </c>
       <c r="E56" s="6" t="n">
         <f aca="false">E55-E54</f>
-        <v>-1.08472253058003</v>
+        <v>-1.92957696663011</v>
       </c>
       <c r="F56" s="6" t="n">
         <f aca="false">F55-F54</f>
-        <v>1.2553914982939</v>
+        <v>-1.32610012005491</v>
       </c>
       <c r="G56" s="6" t="n">
         <f aca="false">G55-G54</f>
-        <v>4.11388174516891</v>
+        <v>-0.791042323327412</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C57" s="6" t="n">
         <v>4.24396782571711</v>
@@ -7883,10 +8061,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>4.11118995206681</v>
@@ -7895,21 +8073,21 @@
         <v>4.19615215761624</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>4.04308428273643</v>
+        <v>3.99649425169988</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>3.99216125299637</v>
+        <v>3.84980326860588</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>3.95524495805184</v>
+        <v>3.68475982495418</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="6" t="n">
         <f aca="false">C58-C57</f>
@@ -7921,23 +8099,23 @@
       </c>
       <c r="E59" s="6" t="n">
         <f aca="false">E58-E57</f>
-        <v>-0.0598177084824716</v>
+        <v>-0.106407739519019</v>
       </c>
       <c r="F59" s="6" t="n">
         <f aca="false">F58-F57</f>
-        <v>0.0692293564107711</v>
+        <v>-0.0731286279797261</v>
       </c>
       <c r="G59" s="6" t="n">
         <f aca="false">G58-G57</f>
-        <v>0.226862604976304</v>
+        <v>-0.043622528121356</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>5.80140530861125</v>
@@ -7957,10 +8135,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61" s="6" t="n">
         <v>3.52641540303952</v>
@@ -7969,21 +8147,21 @@
         <v>3.96540714848889</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>5.20160600358495</v>
+        <v>4.40334159857142</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>6.89137763166116</v>
+        <v>4.45224399770285</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>8.81131563327092</v>
+        <v>4.17687669787226</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C62" s="6" t="n">
         <f aca="false">C61-C60</f>
@@ -7995,23 +8173,23 @@
       </c>
       <c r="E62" s="6" t="n">
         <f aca="false">E61-E60</f>
-        <v>-1.02490482209755</v>
+        <v>-1.82316922711109</v>
       </c>
       <c r="F62" s="6" t="n">
         <f aca="false">F61-F60</f>
-        <v>1.18616214188312</v>
+        <v>-1.25297149207519</v>
       </c>
       <c r="G62" s="6" t="n">
         <f aca="false">G61-G60</f>
-        <v>3.88701914019261</v>
+        <v>-0.747419795206055</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C63" s="6" t="n">
         <v>-2.80615562866419</v>
@@ -8031,10 +8209,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64" s="6" t="n">
         <v>-5.18807878300777</v>
@@ -8043,21 +8221,21 @@
         <v>-5.20559682625485</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-3.31291278163267</v>
+        <v>-4.23159148492751</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-1.37991408025278</v>
+        <v>-4.0378532180395</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0.938475958407936</v>
+        <v>-4.19733739164543</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65" s="6" t="n">
         <f aca="false">C64-C63</f>
@@ -8069,23 +8247,23 @@
       </c>
       <c r="E65" s="6" t="n">
         <f aca="false">E64-E63</f>
-        <v>-1.1882085662826</v>
+        <v>-2.10688726957744</v>
       </c>
       <c r="F65" s="6" t="n">
         <f aca="false">F64-F63</f>
-        <v>0.975660702278887</v>
+        <v>-1.68227843550784</v>
       </c>
       <c r="G65" s="6" t="n">
         <f aca="false">G64-G63</f>
-        <v>3.93472450700067</v>
+        <v>-1.20108884305269</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C66" s="6" t="n">
         <v>1675</v>
@@ -8105,10 +8283,10 @@
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C67" s="6" t="n">
         <v>1675</v>
@@ -8128,10 +8306,10 @@
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" s="6" t="n">
         <f aca="false">C67-C66</f>
@@ -8156,10 +8334,10 @@
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C69" s="6" t="n">
         <v>11.2</v>
@@ -8179,10 +8357,10 @@
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C70" s="6" t="n">
         <v>8.41621326647324</v>
@@ -8191,21 +8369,21 @@
         <v>8.78712095313968</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>10.1287899807039</v>
+        <v>9.06079993265069</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>12.6972629009115</v>
+        <v>9.20714052968951</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>16.465206537042</v>
+        <v>9.35297363159967</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6" t="n">
         <f aca="false">C70-C69</f>
@@ -8217,23 +8395,23 @@
       </c>
       <c r="E71" s="6" t="n">
         <f aca="false">E70-E69</f>
-        <v>-1.37121001929607</v>
+        <v>-2.43920006734932</v>
       </c>
       <c r="F71" s="6" t="n">
         <f aca="false">F70-F69</f>
-        <v>1.69726290091151</v>
+        <v>-1.79285947031049</v>
       </c>
       <c r="G71" s="6" t="n">
         <f aca="false">G70-G69</f>
-        <v>5.96520653704195</v>
+        <v>-1.14702636840033</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C72" s="6" t="n">
         <v>10.64</v>
@@ -8253,10 +8431,10 @@
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C73" s="6" t="n">
         <v>7.99540260314958</v>
@@ -8265,21 +8443,21 @@
         <v>8.3477649054827</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>9.5210625818617</v>
+        <v>8.51715193669164</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>11.8084544978477</v>
+        <v>8.56264069261124</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>15.1479900140786</v>
+        <v>8.6047357410717</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C74" s="6" t="n">
         <f aca="false">C73-C72</f>
@@ -8291,23 +8469,23 @@
       </c>
       <c r="E74" s="6" t="n">
         <f aca="false">E73-E72</f>
-        <v>-1.2889374181383</v>
+        <v>-2.29284806330836</v>
       </c>
       <c r="F74" s="6" t="n">
         <f aca="false">F73-F72</f>
-        <v>1.5784544978477</v>
+        <v>-1.66735930738876</v>
       </c>
       <c r="G74" s="6" t="n">
         <f aca="false">G73-G72</f>
-        <v>5.4879900140786</v>
+        <v>-1.0552642589283</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C75" s="6" t="n">
         <v>11.0739648243069</v>
@@ -8327,10 +8505,10 @@
     </row>
     <row r="76" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C76" s="6" t="n">
         <v>11.0739648243069</v>
@@ -8350,10 +8528,10 @@
     </row>
     <row r="77" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77" s="6" t="n">
         <f aca="false">C76-C75</f>
@@ -8378,10 +8556,10 @@
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C78" s="6" t="n">
         <v>1.01138121510161</v>
@@ -8401,10 +8579,10 @@
     </row>
     <row r="79" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" s="6" t="n">
         <v>0.76</v>
@@ -8413,21 +8591,21 @@
         <v>0.76</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>0.849580659826248</v>
+        <v>0.76</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1.0480908566102</v>
+        <v>0.76</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>1.33792283192951</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C80" s="6" t="n">
         <f aca="false">C79-C78</f>
@@ -8439,23 +8617,23 @@
       </c>
       <c r="E80" s="6" t="n">
         <f aca="false">E79-E78</f>
-        <v>-0.115014085115126</v>
+        <v>-0.204594744941373</v>
       </c>
       <c r="F80" s="6" t="n">
         <f aca="false">F79-F78</f>
-        <v>0.140099936623455</v>
+        <v>-0.147990919986743</v>
       </c>
       <c r="G80" s="6" t="n">
         <f aca="false">G79-G78</f>
-        <v>0.484718245418222</v>
+        <v>-0.0932045865112905</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C81" s="6" t="n">
         <v>0.672768</v>
@@ -8475,10 +8653,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C82" s="6" t="n">
         <v>0.672768</v>
@@ -8498,10 +8676,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C83" s="6" t="n">
         <f aca="false">C82-C81</f>
@@ -8526,10 +8704,10 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C84" s="6" t="n">
         <v>0.936206901352657</v>
@@ -8549,10 +8727,10 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C85" s="6" t="n">
         <v>0.936206901352657</v>
@@ -8572,10 +8750,10 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C86" s="6" t="n">
         <f aca="false">C85-C84</f>
@@ -8600,10 +8778,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C87" s="6" t="n">
         <v>0.325</v>
@@ -8623,10 +8801,10 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C88" s="6" t="n">
         <v>0.325</v>
@@ -8646,10 +8824,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C89" s="6" t="n">
         <f aca="false">C88-C87</f>
@@ -8674,10 +8852,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C90" s="6" t="n">
         <v>0.156034483558776</v>
@@ -8697,10 +8875,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C91" s="6" t="n">
         <v>0.156034483558776</v>
@@ -8720,10 +8898,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92" s="6" t="n">
         <f aca="false">C91-C90</f>
@@ -8748,10 +8926,10 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C93" s="6" t="n">
         <v>1.6</v>
@@ -8771,10 +8949,10 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C94" s="6" t="n">
         <v>1.6</v>
@@ -8794,10 +8972,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" s="6" t="n">
         <f aca="false">C94-C93</f>
@@ -8822,10 +9000,10 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C96" s="9" t="n">
         <v>0.577520140967778</v>
@@ -8845,10 +9023,10 @@
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C97" s="9" t="n">
         <v>0.46171741522123</v>
@@ -8857,44 +9035,44 @@
         <v>0.485863913960979</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>0.562658763299117</v>
+        <v>0.524217577231488</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>0.633192723864468</v>
+        <v>0.53628266075657</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>0.690187115804694</v>
+        <v>0.531298627931297</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="E99" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="F99" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="G99" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B100" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="B100" s="0" t="s">
-        <v>30</v>
       </c>
       <c r="C100" s="6" t="n">
         <v>10.0453731343284</v>
@@ -8914,10 +9092,10 @@
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C101" s="6" t="n">
         <v>7.63760535510633</v>
@@ -8926,21 +9104,21 @@
         <v>8.16155930610514</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>9.90877211091397</v>
+        <v>8.34313270314851</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>11.9891515434083</v>
+        <v>8.08544262852348</v>
       </c>
       <c r="G101" s="6" t="n">
-        <v>13.5100871574208</v>
+        <v>7.54212202903884</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C102" s="6" t="n">
         <f aca="false">C101-C100</f>
@@ -8952,23 +9130,23 @@
       </c>
       <c r="E102" s="6" t="n">
         <f aca="false">E101-E100</f>
-        <v>-0.324578538436676</v>
+        <v>-1.89021794620214</v>
       </c>
       <c r="F102" s="6" t="n">
         <f aca="false">F101-F100</f>
-        <v>2.64758732322482</v>
+        <v>-1.25612159166001</v>
       </c>
       <c r="G102" s="6" t="n">
         <f aca="false">G101-G100</f>
-        <v>5.24199624832992</v>
+        <v>-0.725968880052069</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C103" s="6" t="n">
         <v>9.68716417910448</v>
@@ -8988,10 +9166,10 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C104" s="6" t="n">
         <v>7.27939639988245</v>
@@ -9000,21 +9178,21 @@
         <v>7.75751890206473</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>9.44123964338151</v>
+        <v>7.87560023561604</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>11.4753900755184</v>
+        <v>7.57168116063357</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>12.9786186259523</v>
+        <v>7.01065349757031</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C105" s="6" t="n">
         <f aca="false">C104-C103</f>
@@ -9026,23 +9204,23 @@
       </c>
       <c r="E105" s="6" t="n">
         <f aca="false">E104-E103</f>
-        <v>-0.324578538436676</v>
+        <v>-1.89021794620214</v>
       </c>
       <c r="F105" s="6" t="n">
         <f aca="false">F104-F103</f>
-        <v>2.64758732322481</v>
+        <v>-1.25612159166001</v>
       </c>
       <c r="G105" s="6" t="n">
         <f aca="false">G104-G103</f>
-        <v>5.24199624832991</v>
+        <v>-0.725968880052071</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C106" s="6" t="n">
         <v>4.24396782571711</v>
@@ -9062,10 +9240,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C107" s="6" t="n">
         <v>4.11118995206681</v>
@@ -9074,21 +9252,21 @@
         <v>4.19615215761624</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>4.13545828791215</v>
+        <v>4.04912011474605</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>4.07466749681721</v>
+        <v>3.85939500520026</v>
       </c>
       <c r="G107" s="6" t="n">
-        <v>3.97799392325069</v>
+        <v>3.64888672005448</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C108" s="6" t="n">
         <f aca="false">C107-C106</f>
@@ -9100,23 +9278,23 @@
       </c>
       <c r="E108" s="6" t="n">
         <f aca="false">E107-E106</f>
-        <v>-0.0178990883332082</v>
+        <v>-0.104237261499302</v>
       </c>
       <c r="F108" s="6" t="n">
         <f aca="false">F107-F106</f>
-        <v>0.146002873746767</v>
+        <v>-0.0692696178701819</v>
       </c>
       <c r="G108" s="6" t="n">
         <f aca="false">G107-G106</f>
-        <v>0.289073191170038</v>
+        <v>-0.040034012026172</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C109" s="6" t="n">
         <v>5.80140530861125</v>
@@ -9136,10 +9314,10 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C110" s="6" t="n">
         <v>3.52641540303952</v>
@@ -9148,21 +9326,21 @@
         <v>3.96540714848889</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>5.77331382300183</v>
+        <v>4.29401258840246</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>7.91448404659109</v>
+        <v>4.22604762332321</v>
       </c>
       <c r="G110" s="6" t="n">
-        <v>9.53209323417014</v>
+        <v>3.89323530898436</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C111" s="6" t="n">
         <f aca="false">C110-C109</f>
@@ -9174,23 +9352,23 @@
       </c>
       <c r="E111" s="6" t="n">
         <f aca="false">E110-E109</f>
-        <v>-0.306679450103466</v>
+        <v>-1.78598068470284</v>
       </c>
       <c r="F111" s="6" t="n">
         <f aca="false">F110-F109</f>
-        <v>2.50158444947805</v>
+        <v>-1.18685197378983</v>
       </c>
       <c r="G111" s="6" t="n">
         <f aca="false">G110-G109</f>
-        <v>4.95292305715988</v>
+        <v>-0.685934868025898</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C112" s="6" t="n">
         <v>-2.80615562866419</v>
@@ -9210,10 +9388,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C113" s="6" t="n">
         <v>-5.18807878300777</v>
@@ -9222,21 +9400,21 @@
         <v>-5.52529394546173</v>
       </c>
       <c r="E113" s="6" t="n">
-        <v>-3.58795934904055</v>
+        <v>-5.45442467340792</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>-1.12894887136698</v>
+        <v>-5.48971527525039</v>
       </c>
       <c r="G113" s="6" t="n">
-        <v>1.15716516648437</v>
+        <v>-5.50814237172957</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C114" s="6" t="n">
         <f aca="false">C113-C112</f>
@@ -9248,23 +9426,23 @@
       </c>
       <c r="E114" s="6" t="n">
         <f aca="false">E113-E112</f>
-        <v>-0.45773418013192</v>
+        <v>-2.32419950449929</v>
       </c>
       <c r="F114" s="6" t="n">
         <f aca="false">F113-F112</f>
-        <v>2.61915997128338</v>
+        <v>-1.74160643260003</v>
       </c>
       <c r="G114" s="6" t="n">
         <f aca="false">G113-G112</f>
-        <v>5.47067277161455</v>
+        <v>-1.19463476659939</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C115" s="6" t="n">
         <v>1675</v>
@@ -9284,10 +9462,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C116" s="6" t="n">
         <v>1675</v>
@@ -9307,10 +9485,10 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C117" s="6" t="n">
         <f aca="false">C116-C115</f>
@@ -9335,10 +9513,10 @@
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C118" s="6" t="n">
         <v>11.2</v>
@@ -9358,10 +9536,10 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C119" s="6" t="n">
         <v>8.41621326647324</v>
@@ -9370,21 +9548,21 @@
         <v>8.78712095313968</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>11.0896941906419</v>
+        <v>9.11054009296091</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>14.5791075173507</v>
+        <v>9.30192787524722</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>18.1006394337198</v>
+        <v>9.44738045660847</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C120" s="6" t="n">
         <f aca="false">C119-C118</f>
@@ -9396,23 +9574,23 @@
       </c>
       <c r="E120" s="6" t="n">
         <f aca="false">E119-E118</f>
-        <v>-0.41030580935815</v>
+        <v>-2.38945990703909</v>
       </c>
       <c r="F120" s="6" t="n">
         <f aca="false">F119-F118</f>
-        <v>3.5791075173507</v>
+        <v>-1.69807212475278</v>
       </c>
       <c r="G120" s="6" t="n">
         <f aca="false">G119-G118</f>
-        <v>7.60063943371976</v>
+        <v>-1.05261954339153</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C121" s="6" t="n">
         <v>10.64</v>
@@ -9432,10 +9610,10 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C122" s="6" t="n">
         <v>7.99540260314958</v>
@@ -9444,21 +9622,21 @@
         <v>8.3477649054827</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>10.4243125392033</v>
+        <v>8.56390768738326</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>13.5585699911362</v>
+        <v>8.65079292397992</v>
       </c>
       <c r="G122" s="6" t="n">
-        <v>16.6525882790222</v>
+        <v>8.6915900200798</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C123" s="6" t="n">
         <f aca="false">C122-C121</f>
@@ -9470,23 +9648,23 @@
       </c>
       <c r="E123" s="6" t="n">
         <f aca="false">E122-E121</f>
-        <v>-0.385687460796671</v>
+        <v>-2.24609231261674</v>
       </c>
       <c r="F123" s="6" t="n">
         <f aca="false">F122-F121</f>
-        <v>3.32856999113616</v>
+        <v>-1.57920707602008</v>
       </c>
       <c r="G123" s="6" t="n">
         <f aca="false">G122-G121</f>
-        <v>6.99258827902218</v>
+        <v>-0.968409979920205</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C124" s="6" t="n">
         <v>11.0739648243069</v>
@@ -9506,10 +9684,10 @@
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125" s="6" t="n">
         <v>11.0739648243069</v>
@@ -9529,10 +9707,10 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C126" s="6" t="n">
         <f aca="false">C125-C124</f>
@@ -9557,10 +9735,10 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C127" s="6" t="n">
         <v>1.01138121510161</v>
@@ -9580,10 +9758,10 @@
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C128" s="6" t="n">
         <v>0.76</v>
@@ -9592,21 +9770,21 @@
         <v>0.76</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>0.925100762291762</v>
+        <v>0.76</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>1.19116401049197</v>
+        <v>0.76</v>
       </c>
       <c r="G128" s="6" t="n">
-        <v>1.45611643701766</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C129" s="6" t="n">
         <f aca="false">C128-C127</f>
@@ -9618,23 +9796,23 @@
       </c>
       <c r="E129" s="6" t="n">
         <f aca="false">E128-E127</f>
-        <v>-0.0342276541160419</v>
+        <v>-0.199328416407804</v>
       </c>
       <c r="F129" s="6" t="n">
         <f aca="false">F128-F127</f>
-        <v>0.292425586358811</v>
+        <v>-0.13873842413316</v>
       </c>
       <c r="G129" s="6" t="n">
         <f aca="false">G128-G127</f>
-        <v>0.611437847365018</v>
+        <v>-0.0846785896526444</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C130" s="6" t="n">
         <v>0.672768</v>
@@ -9654,10 +9832,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C131" s="6" t="n">
         <v>0.672768</v>
@@ -9677,10 +9855,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C132" s="6" t="n">
         <f aca="false">C131-C130</f>
@@ -9705,10 +9883,10 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C133" s="6" t="n">
         <v>0.936206901352657</v>
@@ -9728,10 +9906,10 @@
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C134" s="6" t="n">
         <v>0.936206901352657</v>
@@ -9751,10 +9929,10 @@
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C135" s="6" t="n">
         <f aca="false">C134-C133</f>
@@ -9779,10 +9957,10 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C136" s="6" t="n">
         <v>0.325</v>
@@ -9802,10 +9980,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C137" s="6" t="n">
         <v>0.325</v>
@@ -9825,10 +10003,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C138" s="6" t="n">
         <f aca="false">C137-C136</f>
@@ -9853,10 +10031,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C139" s="6" t="n">
         <v>0.156034483558776</v>
@@ -9876,10 +10054,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C140" s="6" t="n">
         <v>0.156034483558776</v>
@@ -9899,10 +10077,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C141" s="6" t="n">
         <f aca="false">C140-C139</f>
@@ -9927,10 +10105,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C142" s="6" t="n">
         <v>1.6</v>
@@ -9950,10 +10128,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C143" s="6" t="n">
         <v>1.6</v>
@@ -9973,10 +10151,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C144" s="6" t="n">
         <f aca="false">C143-C142</f>
@@ -10001,10 +10179,10 @@
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C145" s="9" t="n">
         <v>0.577520140967778</v>
@@ -10024,10 +10202,10 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C146" s="9" t="n">
         <v>0.46171741522123</v>
@@ -10036,13 +10214,13 @@
         <v>0.485863913960979</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>0.582646745568287</v>
+        <v>0.514676290211948</v>
       </c>
       <c r="F146" s="9" t="n">
-        <v>0.660137126295857</v>
+        <v>0.522673626848176</v>
       </c>
       <c r="G146" s="9" t="n">
-        <v>0.705553792740289</v>
+        <v>0.51619892836453</v>
       </c>
     </row>
   </sheetData>
@@ -10061,7 +10239,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="70"/>
@@ -10069,27 +10247,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>11.0739648243069</v>
@@ -10109,7 +10287,7 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>13.19175</v>
@@ -10129,7 +10307,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>1525</v>
@@ -10149,7 +10327,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>6.09649448490156</v>
@@ -10169,7 +10347,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>2.16382546275903</v>
@@ -10188,254 +10366,254 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.938723157532771</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0.787354912031537</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0.527215011304078</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.76</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C9" s="6" t="n">
         <v>0.76</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0.821276842467229</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.972645087968463</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>1.23278498869592</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="D9" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B10" s="6" t="n">
         <v>8.41621326647324</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C10" s="6" t="n">
         <v>8.78712095313968</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>9.77135471571617</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>11.7202982930551</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>15.0376329077242</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>-0.248552386922032</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>-0.23590252581394</v>
-      </c>
       <c r="D10" s="6" t="n">
-        <v>-0.150316981242072</v>
+        <v>9.0422975541778</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.0654816630050099</v>
+        <v>9.15794138366193</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.432155515021352</v>
+        <v>9.27055497484596</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>19.1007066129953</v>
+        <v>-0.248552386922032</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>24.166048949397</v>
+        <v>-0.23590252581394</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>29.0719738716094</v>
+        <v>-0.213713256158452</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>32.3330716619887</v>
+        <v>-0.167459874212552</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>35.0300984760227</v>
+        <v>-0.117090002395623</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>19.1007066129953</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>24.166048949397</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>29.0719738716094</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>32.3330716619887</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>35.0300984760227</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B13" s="6" t="n">
         <v>0.418591980137</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C13" s="6" t="n">
         <v>0.345433584238891</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0.315942545674307</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.337112338923101</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0.394935294988558</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="D13" s="6" t="n">
+        <v>0.292369542517637</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.263410961254825</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.243473782487255</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>11.0739648243069</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>11.5620012541312</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>11.9221051745404</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>12.1146585916967</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>12.3065442521048</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>13.19175</v>
+        <v>11.0739648243069</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>26.3835</v>
+        <v>11.5620012541312</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>25.74</v>
+        <v>11.9221051745404</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>25.0965</v>
+        <v>12.1146585916967</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>17.69625</v>
+        <v>12.3065442521048</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1525</v>
+        <v>13.19175</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2300</v>
+        <v>26.3835</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3319.5</v>
+        <v>25.74</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>4117</v>
+        <v>25.0965</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4872.5</v>
+        <v>17.69625</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1525</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3319.5</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4117</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>4872.5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>6.09649448490156</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>19.1998592826102</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>28.2726858538479</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>35.2523917314805</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>41.9265748983718</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>6.09649448490156</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>19.1998592826102</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>28.2726858538479</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>35.2523917314805</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>41.9265748983718</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="6" t="n">
+      <c r="B20" s="6" t="n">
         <v>2.16382546275903</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C20" s="6" t="n">
         <v>1.37415069619266</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>0.910419340173752</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0.711909143389802</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0.422077168070488</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0.910419340173752</v>
@@ -10448,8 +10626,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>56</v>
+      <c r="A21" s="0" t="s">
+        <v>54</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>0.76</v>
@@ -10458,333 +10636,393 @@
         <v>0.76</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.849580659826248</v>
+        <v>0.76</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1.0480908566102</v>
+        <v>0.76</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.33792283192951</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>57</v>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8.41621326647324</v>
+        <v>0</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>8.78712095313968</v>
+        <v>0</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>10.1287899807039</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>12.6972629009115</v>
+        <v>0</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>16.465206537042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>-0.248552386922032</v>
+        <v>0.76</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>-0.23590252581394</v>
+        <v>0.76</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>-0.119235653851832</v>
+        <v>0.76</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.154296627355592</v>
+        <v>0.76</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.56811490828971</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>59</v>
+      <c r="A24" s="0" t="s">
+        <v>57</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>19.1007066129953</v>
+        <v>8.41621326647324</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>24.166048949397</v>
+        <v>8.78712095313968</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>29.6255436770286</v>
+        <v>9.06079993265069</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>33.823128962171</v>
+        <v>9.20714052968951</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>37.663483762171</v>
+        <v>9.35297363159967</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-0.248552386922032</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.23590252581394</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.212104353682549</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.162987224573681</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.109240606514317</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>19.1007066129953</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>24.166048949397</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>29.6255436770286</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>33.823128962171</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>37.663483762171</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B27" s="6" t="n">
         <v>0.418591980137</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C27" s="6" t="n">
         <v>0.345433584238891</v>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0.321380180754092</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0.349123657691597</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0.402193012991888</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="D27" s="6" t="n">
+        <v>0.287493523479056</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.253159330770019</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.22846361731716</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>11.0739648243069</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>11.5620012541312</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>11.9875527538959</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>12.23937878322</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>12.4307637586954</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>13.19175</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>26.3835</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>25.74</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>25.0965</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>17.69625</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>1525</v>
+        <v>11.0739648243069</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>2300</v>
+        <v>11.5620012541312</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>3600</v>
+        <v>11.9875527538959</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>5100</v>
+        <v>12.23937878322</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>6700</v>
+        <v>12.4307637586954</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>6.09649448490156</v>
+        <v>13.19175</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>19.1998592826102</v>
+        <v>26.3835</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>30.8300676745797</v>
+        <v>25.74</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>44.1190439122976</v>
+        <v>25.0965</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>58.2336531345346</v>
+        <v>17.69625</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>54</v>
+      <c r="A32" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2.16382546275903</v>
+        <v>1525</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1.37415069619266</v>
+        <v>2300</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>0.834899237708238</v>
+        <v>3600</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.56883598950803</v>
+        <v>5100</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.303883562982338</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1</v>
+        <v>6.09649448490156</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1</v>
+        <v>19.1998592826102</v>
       </c>
       <c r="D33" s="6" t="n">
+        <v>30.8300676745797</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>44.1190439122976</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>58.2336531345346</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2.16382546275903</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1.37415069619266</v>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>0.834899237708238</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E34" s="6" t="n">
         <v>0.56883598950803</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>0.303883562982338</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>0.925100762291762</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>1.19116401049197</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>1.45611643701766</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>8.41621326647324</v>
+        <v>0.76</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>8.78712095313968</v>
+        <v>0.76</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>11.0896941906419</v>
+        <v>0.76</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>14.5791075173507</v>
+        <v>0.76</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>18.1006394337198</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>-0.248552386922032</v>
+        <v>0</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>-0.23590252581394</v>
+        <v>0</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>-0.035678766031144</v>
+        <v>0</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.325373410668246</v>
+        <v>0</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.723870422259025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>8.41621326647324</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>8.78712095313968</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>9.11054009296091</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>9.30192787524722</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>9.44738045660847</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>-0.248552386922032</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>-0.23590252581394</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>-0.207779122351225</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>-0.154370193159343</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>-0.100249480323003</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B40" s="6" t="n">
         <v>19.1007066129953</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C40" s="6" t="n">
         <v>24.166048949397</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D40" s="6" t="n">
         <v>31.1137118552337</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E40" s="6" t="n">
         <v>36.6938815588524</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F40" s="6" t="n">
         <v>40.6799069081226</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+    <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B41" s="6" t="n">
         <v>0.418591980137</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C41" s="6" t="n">
         <v>0.345433584238891</v>
       </c>
-      <c r="D38" s="6" t="n">
-        <v>0.335039181043577</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>0.369504926029423</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>0.409356597512202</v>
+      <c r="D41" s="6" t="n">
+        <v>0.27524545214115</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>0.235755732467418</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>0.21365806071558</v>
       </c>
     </row>
   </sheetData>
@@ -11554,7 +11792,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -11588,22 +11826,22 @@
         <v>171</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.2392623465329</v>
+        <v>13.9805355188478</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>98.0184876310382</v>
+        <v>5.24785180769839</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>131.856409498704</v>
+        <v>0</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>30.2923738695558</v>
+        <v>54.8411224358677</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>67.5253862342037</v>
+        <v>104.768016723937</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>118.117303569076</v>
+        <v>183.494127989618</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11611,22 +11849,22 @@
         <v>172</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>4.53518527221571</v>
+        <v>64.6669188000141</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.210584589014922</v>
+        <v>39.9921714449852</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>10.9107429507562</v>
+        <v>26.6131872937555</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>48.7638046090247</v>
+        <v>22.3038876059962</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>85.7998100703005</v>
+        <v>63.2751720701874</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>136.138531772961</v>
+        <v>125.69196273427</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11634,22 +11872,22 @@
         <v>173</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>541.463576905594</v>
+        <v>0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>605.657805554812</v>
+        <v>0</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>774.807525039785</v>
+        <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0</v>
+        <v>106.972116305001</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0</v>
+        <v>167.529513861542</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0</v>
+        <v>265.765609193848</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11703,22 +11941,22 @@
         <v>177</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>98.0393682730865</v>
+        <v>14.196218670304</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>104.230559559731</v>
+        <v>0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>142.07182256497</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>34.4356245860338</v>
+        <v>60.8974299103196</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>82.5004922590829</v>
+        <v>123.816515240069</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>146.089658397616</v>
+        <v>219.443184746294</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11726,22 +11964,22 @@
         <v>178</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>72.3072544217536</v>
+        <v>15.3814820255223</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>75.0499694336637</v>
+        <v>0</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>103.336776099537</v>
+        <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>35.827535439159</v>
+        <v>59.4078843781145</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>73.9419743341977</v>
+        <v>109.715394667943</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>126.48753038466</v>
+        <v>189.285122651721</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11749,22 +11987,22 @@
         <v>179</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>53.4606709984488</v>
+        <v>8.98740713182911</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>59.2368892738512</v>
+        <v>0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>96.1247658795772</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>42.4939949293803</v>
+        <v>62.5727599474417</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>80.3005817727207</v>
+        <v>113.215855627927</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>130.892063755311</v>
+        <v>193.630043114125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11772,22 +12010,22 @@
         <v>180</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>226.818406762832</v>
+        <v>35.486676414374</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>236.097075008715</v>
+        <v>25.4591641583472</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>283.36796051488</v>
+        <v>6.54143899358953</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0</v>
+        <v>38.1883765550662</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>29.5015796743946</v>
+        <v>86.4650938768602</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>80.0942627510114</v>
+        <v>161.533791894029</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11795,45 +12033,45 @@
         <v>181</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>62.4126178125471</v>
+        <v>74.1511544138331</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>54.1588765985846</v>
+        <v>45.1420478144943</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>63.1734242877632</v>
+        <v>28.7678111436979</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>36.6746992676367</v>
+        <v>24.0981266922476</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>77.2079481506143</v>
+        <v>70.9785806333937</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>135.114480565557</v>
+        <v>142.952604998093</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="7" t="s">
         <v>182</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>150.35416510844</v>
+        <v>30.4934015887655</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>188.003533786384</v>
+        <v>20.1619489999589</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>274.720290467913</v>
+        <v>0.976496192665392</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>17.0372440100219</v>
+        <v>42.0312488751774</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>47.4160846984632</v>
+        <v>90.6887708716529</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>82.8163422221394</v>
+        <v>166.601479146001</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11841,45 +12079,22 @@
         <v>183</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>178.621464305709</v>
+        <v>55.5248798507141</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>201.313153760705</v>
+        <v>36.5923274810978</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>257.225312528425</v>
+        <v>20.2985703805962</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>10.9371817050411</v>
+        <v>29.2218071632103</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>45.6319007306999</v>
+        <v>76.6099899603162</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>90.5976628066016</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <v>13.9805355188478</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>5.24785180769839</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="0" t="n">
-        <v>54.8411224358677</v>
-      </c>
-      <c r="F14" s="0" t="n">
-        <v>104.768016723937</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>183.494127989618</v>
+        <v>149.70934530059</v>
       </c>
     </row>
   </sheetData>
@@ -11912,16 +12127,16 @@
         <v>151</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11929,7 +12144,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>0</v>
@@ -11940,7 +12155,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>0</v>
@@ -11951,7 +12166,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>0</v>
@@ -11962,7 +12177,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>30.1583812031264</v>
@@ -11982,19 +12197,19 @@
         <v>10</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>17.0881079326997</v>
+        <v>-60.1706188949854</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>74.96806893125</v>
+        <v>-33.1053250195911</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>-30.2682237933868</v>
+        <v>-82.3149502475807</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>6.19424717730819</v>
+        <v>30.7429957436201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12002,7 +12217,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>0</v>
@@ -12026,7 +12241,7 @@
       </c>
       <c r="C8" s="0" t="n">
         <f aca="false">SUM(C2:C7)</f>
-        <v>47.2464891358262</v>
+        <v>-30.0122376918589</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12034,10 +12249,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>47.2464891358262</v>
+        <v>-30.0122376918589</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12045,7 +12260,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C10" s="0" t="str">
         <f aca="false">IF(ABS(C8-C9)&lt;0.01,"通過","不通過")</f>
@@ -12054,10 +12269,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C12" s="0" t="n">
         <v>0</v>
@@ -12065,10 +12280,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>0</v>
@@ -12076,10 +12291,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>0</v>
@@ -12087,10 +12302,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>15.4635753176099</v>
@@ -12107,30 +12322,30 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>52.8764398165439</v>
+        <v>-39.8941960067959</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>122.339248235835</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>-3.95676707196671</v>
+        <v>-76.8285987641094</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>-3.45319439918997</v>
+        <v>33.7894360905433</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>0</v>
@@ -12147,33 +12362,33 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>160</v>
       </c>
       <c r="C18" s="0" t="n">
         <f aca="false">SUM(C12:C17)</f>
-        <v>68.3400151341538</v>
+        <v>-24.430620689186</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>68.3400151341538</v>
+        <v>-24.430620689186</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20" s="0" t="str">
         <f aca="false">IF(ABS(C18-C19)&lt;0.01,"通過","不通過")</f>
@@ -12182,10 +12397,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>0</v>
@@ -12193,10 +12408,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>0</v>
@@ -12204,10 +12419,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>0</v>
@@ -12215,10 +12430,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>8.81889083955124</v>
@@ -12235,30 +12450,30 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>103.088598355006</v>
+        <v>-28.7678111436979</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>171.562509646096</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>47.0644891168407</v>
+        <v>-52.3051111703597</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>-24.835301429017</v>
+        <v>40.5415229915257</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>0</v>
@@ -12275,33 +12490,33 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>160</v>
       </c>
       <c r="C28" s="0" t="n">
         <f aca="false">SUM(C22:C27)</f>
-        <v>111.907489194557</v>
+        <v>-19.9489203041466</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>111.907489194557</v>
+        <v>-19.9489203041466</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C30" s="0" t="str">
         <f aca="false">IF(ABS(C28-C29)&lt;0.01,"通過","不通過")</f>
